--- a/public/templates/layout_carga_nao_localizados_template.xlsx
+++ b/public/templates/layout_carga_nao_localizados_template.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="55">
   <si>
     <t>Dossiê</t>
   </si>
@@ -191,6 +191,15 @@
   </si>
   <si>
     <t>0020647-60.2022.5.04.0017</t>
+  </si>
+  <si>
+    <t>Reclamante</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>JOSÉ DO EXEMPLO</t>
   </si>
 </sst>
 </file>
@@ -325,12 +334,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -342,9 +354,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -680,45 +689,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AJ4"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="25.796875" customWidth="1"/>
-    <col min="2" max="2" width="22.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43.296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.09765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="47.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46.8984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="44.09765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="99.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.69921875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.09765625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="10.09765625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="80.59765625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="169" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="25.796875" customWidth="1"/>
+    <col min="3" max="3" width="22.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="47.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.8984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="44.09765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="99.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.19921875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="80.59765625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.69921875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.69921875" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="169" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="1" customFormat="1" ht="50.25" customHeight="1">
+    <row r="1" spans="1:36" s="1" customFormat="1" ht="50.25" customHeight="1">
       <c r="A1" s="7" t="s">
         <v>27</v>
       </c>
@@ -739,209 +748,219 @@
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
-      <c r="S1" s="8" t="s">
+      <c r="S1" s="7"/>
+      <c r="T1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="9" t="s">
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="4"/>
+      <c r="AA1" s="10"/>
       <c r="AB1" s="4"/>
-      <c r="AC1" s="10" t="s">
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="AD1" s="10"/>
-      <c r="AE1" s="11" t="s">
+      <c r="AE1" s="11"/>
+      <c r="AF1" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="AF1" s="11"/>
-      <c r="AG1" s="6" t="s">
+      <c r="AG1" s="12"/>
+      <c r="AH1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="AH1" s="6"/>
-      <c r="AI1" s="3" t="s">
+      <c r="AI1" s="8"/>
+      <c r="AJ1" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:35" s="1" customFormat="1" ht="72">
+    <row r="2" spans="1:36" s="1" customFormat="1" ht="72">
       <c r="A2" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:36">
       <c r="A3" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="K3" t="s">
-        <v>39</v>
       </c>
       <c r="L3" t="s">
         <v>39</v>
       </c>
+      <c r="M3" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:36">
       <c r="A4" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="E4" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>39</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>39</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="S1:X1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="T1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
